--- a/data/trans_dic/P39A2_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P39A2_2023-Edad-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que sí diría que sentirse débil mareado o a punto de desmayarse es un síntoma de que a alguien le está dando un ataque al corazón</t>
+          <t>Población que sí diría que sentirse débil mareado o a punto de desmayarse es un síntoma de que a alguien le está dando un ataque al corazón (tasa de respuesta: 90,01%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>70,38; 85,43</t>
+          <t>71,32; 86,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>69,81; 82,76</t>
+          <t>70,28; 83,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>72,81; 82,61</t>
+          <t>73,02; 82,76</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>66,71; 77,87</t>
+          <t>66,94; 78,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>34,14; 70,94</t>
+          <t>36,43; 70,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>48,34; 71,91</t>
+          <t>48,6; 71,42</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>66,93; 75,18</t>
+          <t>66,66; 74,78</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>58,57; 66,02</t>
+          <t>58,78; 66,2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>63,89; 69,55</t>
+          <t>64,18; 69,8</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>67,17; 91,33</t>
+          <t>67,24; 90,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>60,8; 66,92</t>
+          <t>60,7; 66,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>65,24; 82,61</t>
+          <t>65,21; 83,12</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>66,66; 73,94</t>
+          <t>66,8; 74,23</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>67,53; 73,24</t>
+          <t>67,4; 73,68</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>68,08; 72,91</t>
+          <t>67,9; 72,72</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>64,06; 72,38</t>
+          <t>63,94; 72,85</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>69,45; 92,73</t>
+          <t>69,15; 93,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>68,81; 88,82</t>
+          <t>68,85; 87,53</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>64,39; 74,0</t>
+          <t>64,44; 74,04</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>62,06; 69,79</t>
+          <t>62,37; 69,53</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>64,15; 70,37</t>
+          <t>64,13; 70,37</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>70,52; 80,25</t>
+          <t>70,48; 79,71</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>64,1; 74,0</t>
+          <t>63,93; 74,02</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>68,3; 75,17</t>
+          <t>68,02; 75,06</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que sí diría que sentirse débil mareado o a punto de desmayarse es un síntoma de que a alguien le está dando un ataque al corazón</t>
+          <t>Población que sí diría que sentirse débil mareado o a punto de desmayarse es un síntoma de que a alguien le está dando un ataque al corazón (tasa de respuesta: 90,01%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>246664; 299408</t>
+          <t>249953; 304187</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>189095; 224170</t>
+          <t>190358; 224965</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>452381; 513248</t>
+          <t>453653; 514183</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>261360; 305075</t>
+          <t>262272; 306018</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>163193; 339091</t>
+          <t>174117; 336353</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>420461; 625450</t>
+          <t>422745; 621226</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>343972; 386384</t>
+          <t>342587; 384312</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>299843; 337969</t>
+          <t>300903; 338858</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>655426; 713523</t>
+          <t>658341; 716045</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>560824; 762556</t>
+          <t>561428; 757352</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>382746; 421275</t>
+          <t>382079; 420420</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>955321; 1209707</t>
+          <t>954928; 1217172</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>349219; 387383</t>
+          <t>349948; 388875</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>336838; 365322</t>
+          <t>336168; 367515</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>696199; 745672</t>
+          <t>694375; 743650</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>212705; 240305</t>
+          <t>212301; 241877</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>393363; 525208</t>
+          <t>391669; 526739</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>618185; 797948</t>
+          <t>618582; 786400</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>153240; 176099</t>
+          <t>153363; 176207</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>207706; 233575</t>
+          <t>208752; 232723</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>367350; 403006</t>
+          <t>367282; 402993</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2245967; 2556099</t>
+          <t>2244857; 2538854</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2109104; 2434830</t>
+          <t>2103489; 2435349</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>4422301; 4867367</t>
+          <t>4404259; 4859959</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P39A2_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P39A2_2023-Edad-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>79,2%</t>
+          <t>77,9%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>76,75%</t>
+          <t>74,5%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>78,13%</t>
+          <t>76,28%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>71,32; 86,8</t>
+          <t>70,61; 84,49</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>70,28; 83,06</t>
+          <t>67,34; 80,34</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>73,02; 82,76</t>
+          <t>71,1; 80,82</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>72,44%</t>
+          <t>72,48%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>58,83%</t>
+          <t>68,99%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>64,96%</t>
+          <t>70,71%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>66,94; 78,11</t>
+          <t>66,88; 78,15</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>36,43; 70,37</t>
+          <t>64,36; 73,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>48,6; 71,42</t>
+          <t>66,72; 74,0</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>70,98%</t>
+          <t>70,49%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>62,64%</t>
+          <t>62,17%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>66,82%</t>
+          <t>66,33%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>66,66; 74,78</t>
+          <t>66,35; 74,56</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>58,78; 66,2</t>
+          <t>58,61; 65,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>64,18; 69,8</t>
+          <t>63,64; 68,89</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>69,15%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>63,86%</t>
+          <t>63,94%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>71,77%</t>
+          <t>66,45%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>67,24; 90,71</t>
+          <t>64,99; 72,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>60,7; 66,79</t>
+          <t>60,82; 66,51</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>65,21; 83,12</t>
+          <t>64,09; 68,85</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>70,52%</t>
+          <t>69,79%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>70,43%</t>
+          <t>69,7%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>70,48%</t>
+          <t>69,74%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>66,8; 74,23</t>
+          <t>66,14; 73,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>67,4; 73,68</t>
+          <t>66,62; 72,61</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>67,9; 72,72</t>
+          <t>67,51; 72,18</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>68,57%</t>
+          <t>68,67%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>81,12%</t>
+          <t>70,77%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>69,76%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>63,94; 72,85</t>
+          <t>64,65; 73,11</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>69,15; 93,0</t>
+          <t>67,12; 73,99</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>68,85; 87,53</t>
+          <t>67,18; 72,52</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>69,56%</t>
+          <t>69,9%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>66,17%</t>
+          <t>65,78%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>67,58%</t>
+          <t>67,5%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>64,44; 74,04</t>
+          <t>65,09; 74,54</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>62,37; 69,53</t>
+          <t>61,91; 69,39</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>64,13; 70,37</t>
+          <t>64,71; 70,4</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>73,4%</t>
+          <t>70,93%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>68,2%</t>
+          <t>67,28%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>70,76%</t>
+          <t>69,06%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>70,48; 79,71</t>
+          <t>69,14; 72,57</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>63,93; 74,02</t>
+          <t>65,86; 68,54</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>68,02; 75,06</t>
+          <t>68,01; 70,25</t>
         </is>
       </c>
     </row>
@@ -1060,17 +1060,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>277548</t>
+          <t>271710</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>207889</t>
+          <t>235918</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>485437</t>
+          <t>507627</t>
         </is>
       </c>
     </row>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>249953; 304187</t>
+          <t>246263; 294693</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>190358; 224965</t>
+          <t>213268; 254418</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>453653; 514183</t>
+          <t>473123; 537816</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>283805</t>
+          <t>320240</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>281209</t>
+          <t>313477</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>565013</t>
+          <t>633718</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>262272; 306018</t>
+          <t>295482; 345278</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>174117; 336353</t>
+          <t>292441; 333804</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>422745; 621226</t>
+          <t>597992; 663203</t>
         </is>
       </c>
     </row>
@@ -1206,17 +1206,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>364826</t>
+          <t>409469</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>320677</t>
+          <t>361535</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>685503</t>
+          <t>771004</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>342587; 384312</t>
+          <t>385427; 433109</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>300903; 338858</t>
+          <t>340842; 381863</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>658341; 716045</t>
+          <t>739711; 800774</t>
         </is>
       </c>
     </row>
@@ -1279,17 +1279,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>648983</t>
+          <t>439590</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>401965</t>
+          <t>435950</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1050949</t>
+          <t>875540</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>561428; 757352</t>
+          <t>413175; 462117</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>382079; 420420</t>
+          <t>414663; 453433</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>954928; 1217172</t>
+          <t>844370; 907118</t>
         </is>
       </c>
     </row>
@@ -1352,17 +1352,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>369433</t>
+          <t>393930</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>351318</t>
+          <t>385776</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>720752</t>
+          <t>779706</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>349948; 388875</t>
+          <t>373382; 414064</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>336168; 367515</t>
+          <t>368717; 401854</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>694375; 743650</t>
+          <t>754746; 806971</t>
         </is>
       </c>
     </row>
@@ -1425,17 +1425,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>227662</t>
+          <t>251408</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>459435</t>
+          <t>279391</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>687097</t>
+          <t>530800</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>212301; 241877</t>
+          <t>236699; 267677</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>391669; 526739</t>
+          <t>264955; 292076</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>618582; 786400</t>
+          <t>511194; 551786</t>
         </is>
       </c>
     </row>
@@ -1498,17 +1498,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>165536</t>
+          <t>182854</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>221457</t>
+          <t>241192</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>386993</t>
+          <t>424046</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>153363; 176207</t>
+          <t>170263; 194994</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>208752; 232723</t>
+          <t>226982; 254414</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>367282; 402993</t>
+          <t>406526; 442256</t>
         </is>
       </c>
     </row>
@@ -1571,17 +1571,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>2337794</t>
+          <t>2269200</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2243949</t>
+          <t>2253240</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>4581743</t>
+          <t>4522440</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2244857; 2538854</t>
+          <t>2212180; 2321968</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2103489; 2435349</t>
+          <t>2205773; 2295612</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>4404259; 4859959</t>
+          <t>4453543; 4600677</t>
         </is>
       </c>
     </row>
